--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181495</v>
+        <v>121181493</v>
       </c>
       <c r="B20" t="n">
-        <v>98092</v>
+        <v>98713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>222302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181493</v>
+        <v>121181495</v>
       </c>
       <c r="B21" t="n">
-        <v>98713</v>
+        <v>98092</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222302</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181611</v>
+        <v>121181491</v>
       </c>
       <c r="B18" t="n">
-        <v>91249</v>
+        <v>105171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2628,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121181489</v>
+        <v>121181611</v>
       </c>
       <c r="B19" t="n">
-        <v>100246</v>
+        <v>91259</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2735,25 +2735,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181493</v>
+        <v>121181486</v>
       </c>
       <c r="B20" t="n">
-        <v>98713</v>
+        <v>94496</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222302</v>
+        <v>2813</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181495</v>
+        <v>121181483</v>
       </c>
       <c r="B21" t="n">
-        <v>98092</v>
+        <v>91137</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3047,7 +3047,7 @@
         <v>121181487</v>
       </c>
       <c r="B22" t="n">
-        <v>94474</v>
+        <v>94484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181491</v>
+        <v>121181495</v>
       </c>
       <c r="B23" t="n">
-        <v>105161</v>
+        <v>98102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181494</v>
+        <v>121181489</v>
       </c>
       <c r="B24" t="n">
-        <v>97031</v>
+        <v>100256</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3274,16 +3274,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181483</v>
+        <v>121181493</v>
       </c>
       <c r="B25" t="n">
-        <v>91127</v>
+        <v>98723</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
         <v>121181484</v>
       </c>
       <c r="B26" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181486</v>
+        <v>121181494</v>
       </c>
       <c r="B27" t="n">
-        <v>94486</v>
+        <v>97041</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2813</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181493</v>
+        <v>121181484</v>
       </c>
       <c r="B25" t="n">
-        <v>98723</v>
+        <v>90983</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222302</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181484</v>
+        <v>121181493</v>
       </c>
       <c r="B26" t="n">
-        <v>90983</v>
+        <v>98723</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,25 +3484,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>222302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181491</v>
+        <v>121181487</v>
       </c>
       <c r="B18" t="n">
-        <v>105171</v>
+        <v>94484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121181611</v>
+        <v>121181494</v>
       </c>
       <c r="B19" t="n">
-        <v>91259</v>
+        <v>97041</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2735,25 +2735,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181486</v>
+        <v>121181489</v>
       </c>
       <c r="B20" t="n">
-        <v>94496</v>
+        <v>100256</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2813</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181483</v>
+        <v>121181484</v>
       </c>
       <c r="B21" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181487</v>
+        <v>121181491</v>
       </c>
       <c r="B22" t="n">
-        <v>94484</v>
+        <v>105171</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181495</v>
+        <v>121181493</v>
       </c>
       <c r="B23" t="n">
-        <v>98102</v>
+        <v>98723</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>222302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181489</v>
+        <v>121181483</v>
       </c>
       <c r="B24" t="n">
-        <v>100256</v>
+        <v>91137</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3270,25 +3270,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181484</v>
+        <v>121181611</v>
       </c>
       <c r="B25" t="n">
-        <v>90983</v>
+        <v>91259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181493</v>
+        <v>121181486</v>
       </c>
       <c r="B26" t="n">
-        <v>98723</v>
+        <v>94496</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222302</v>
+        <v>2813</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181494</v>
+        <v>121181495</v>
       </c>
       <c r="B27" t="n">
-        <v>97041</v>
+        <v>98102</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181487</v>
+        <v>121181486</v>
       </c>
       <c r="B18" t="n">
-        <v>94484</v>
+        <v>94508</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2726,7 +2726,7 @@
         <v>121181494</v>
       </c>
       <c r="B19" t="n">
-        <v>97041</v>
+        <v>97054</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181489</v>
+        <v>121181483</v>
       </c>
       <c r="B20" t="n">
-        <v>100256</v>
+        <v>91149</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2842,25 +2842,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181484</v>
+        <v>121181611</v>
       </c>
       <c r="B21" t="n">
-        <v>90983</v>
+        <v>91271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181491</v>
+        <v>121181487</v>
       </c>
       <c r="B22" t="n">
-        <v>105171</v>
+        <v>94496</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181493</v>
+        <v>121181495</v>
       </c>
       <c r="B23" t="n">
-        <v>98723</v>
+        <v>98115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222302</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181483</v>
+        <v>121181493</v>
       </c>
       <c r="B24" t="n">
-        <v>91137</v>
+        <v>98736</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3270,25 +3270,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181611</v>
+        <v>121181484</v>
       </c>
       <c r="B25" t="n">
-        <v>91259</v>
+        <v>90995</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181486</v>
+        <v>121181491</v>
       </c>
       <c r="B26" t="n">
-        <v>94496</v>
+        <v>105184</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181495</v>
+        <v>121181489</v>
       </c>
       <c r="B27" t="n">
-        <v>98102</v>
+        <v>100269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181486</v>
+        <v>121181491</v>
       </c>
       <c r="B18" t="n">
-        <v>94508</v>
+        <v>105185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2726,7 +2726,7 @@
         <v>121181494</v>
       </c>
       <c r="B19" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181483</v>
+        <v>121181484</v>
       </c>
       <c r="B20" t="n">
-        <v>91149</v>
+        <v>90996</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2842,25 +2842,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181611</v>
+        <v>121181495</v>
       </c>
       <c r="B21" t="n">
-        <v>91271</v>
+        <v>98116</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181487</v>
+        <v>121181493</v>
       </c>
       <c r="B22" t="n">
-        <v>94496</v>
+        <v>98737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>222302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181495</v>
+        <v>121181611</v>
       </c>
       <c r="B23" t="n">
-        <v>98115</v>
+        <v>91272</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181493</v>
+        <v>121181486</v>
       </c>
       <c r="B24" t="n">
-        <v>98736</v>
+        <v>94509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3274,21 +3274,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>2813</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181484</v>
+        <v>121181483</v>
       </c>
       <c r="B25" t="n">
-        <v>90995</v>
+        <v>91150</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181491</v>
+        <v>121181489</v>
       </c>
       <c r="B26" t="n">
-        <v>105184</v>
+        <v>100270</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181489</v>
+        <v>121181487</v>
       </c>
       <c r="B27" t="n">
-        <v>100269</v>
+        <v>94497</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181491</v>
+        <v>121181494</v>
       </c>
       <c r="B18" t="n">
-        <v>105185</v>
+        <v>97058</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121181494</v>
+        <v>121181493</v>
       </c>
       <c r="B19" t="n">
-        <v>97055</v>
+        <v>98740</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>222302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181484</v>
+        <v>121181491</v>
       </c>
       <c r="B20" t="n">
-        <v>90996</v>
+        <v>105188</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2842,25 +2842,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181495</v>
+        <v>121181487</v>
       </c>
       <c r="B21" t="n">
-        <v>98116</v>
+        <v>94500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181493</v>
+        <v>121181611</v>
       </c>
       <c r="B22" t="n">
-        <v>98737</v>
+        <v>91275</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3056,25 +3056,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222302</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181611</v>
+        <v>121181483</v>
       </c>
       <c r="B23" t="n">
-        <v>91272</v>
+        <v>91153</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
         <v>121181486</v>
       </c>
       <c r="B24" t="n">
-        <v>94509</v>
+        <v>94512</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181483</v>
+        <v>121181484</v>
       </c>
       <c r="B25" t="n">
-        <v>91150</v>
+        <v>90999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
         <v>121181489</v>
       </c>
       <c r="B26" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181487</v>
+        <v>121181495</v>
       </c>
       <c r="B27" t="n">
-        <v>94497</v>
+        <v>98119</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181494</v>
+        <v>121181487</v>
       </c>
       <c r="B18" t="n">
-        <v>97058</v>
+        <v>94500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121181493</v>
+        <v>121181494</v>
       </c>
       <c r="B19" t="n">
-        <v>98740</v>
+        <v>97058</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222302</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181491</v>
+        <v>121181495</v>
       </c>
       <c r="B20" t="n">
-        <v>105188</v>
+        <v>98119</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181487</v>
+        <v>121181493</v>
       </c>
       <c r="B21" t="n">
-        <v>94500</v>
+        <v>98740</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>222302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181483</v>
+        <v>121181484</v>
       </c>
       <c r="B23" t="n">
-        <v>91153</v>
+        <v>90999</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181486</v>
+        <v>121181491</v>
       </c>
       <c r="B24" t="n">
-        <v>94512</v>
+        <v>105188</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3274,21 +3274,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2813</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181484</v>
+        <v>121181486</v>
       </c>
       <c r="B25" t="n">
-        <v>90999</v>
+        <v>94512</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,25 +3377,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181495</v>
+        <v>121181483</v>
       </c>
       <c r="B27" t="n">
-        <v>98119</v>
+        <v>91153</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3591,25 +3591,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -2616,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181487</v>
+        <v>121181611</v>
       </c>
       <c r="B18" t="n">
-        <v>94500</v>
+        <v>91281</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2628,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2726,7 +2726,7 @@
         <v>121181494</v>
       </c>
       <c r="B19" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>121181495</v>
       </c>
       <c r="B20" t="n">
-        <v>98119</v>
+        <v>98125</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181493</v>
+        <v>121181484</v>
       </c>
       <c r="B21" t="n">
-        <v>98740</v>
+        <v>91005</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,25 +2949,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222302</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181611</v>
+        <v>121181483</v>
       </c>
       <c r="B22" t="n">
-        <v>91275</v>
+        <v>91159</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181484</v>
+        <v>121181487</v>
       </c>
       <c r="B23" t="n">
-        <v>90999</v>
+        <v>94506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3261,7 +3261,7 @@
         <v>121181491</v>
       </c>
       <c r="B24" t="n">
-        <v>105188</v>
+        <v>105194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>121181486</v>
       </c>
       <c r="B25" t="n">
-        <v>94512</v>
+        <v>94518</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181489</v>
+        <v>121181493</v>
       </c>
       <c r="B26" t="n">
-        <v>100273</v>
+        <v>98746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,21 +3488,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>222302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121181483</v>
+        <v>121181489</v>
       </c>
       <c r="B27" t="n">
-        <v>91153</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3591,25 +3591,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60185565</v>
+        <v>62066117</v>
       </c>
       <c r="B2" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
+          <t>Vägskälet 1, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R2" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Flera Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,65 +765,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jörgen Sundin, Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61298441</v>
+        <v>62066119</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
+          <t>Vägskälet 1, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R3" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,65 +871,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jörgen Sundin, Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61047668</v>
+        <v>62255426</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
+          <t>Vägskälet 1, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R4" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,100 +952,94 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området, Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>Barrnaturskog</t>
         </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61057592</v>
+        <v>62066123</v>
       </c>
       <c r="B5" t="n">
-        <v>96943</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222302</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
+          <t>Vägskälet 1, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R5" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1063,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,66 +1084,75 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlågor, asplåga,</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Granlågor, asplåga,</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61380396</v>
+        <v>121181484</v>
       </c>
       <c r="B6" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
+          <t>Vilmyren, 200 m NO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472730.423935426</v>
+        <v>472560</v>
       </c>
       <c r="R6" t="n">
-        <v>7071107.92135937</v>
+        <v>7070988</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,27 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1997-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Urskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,53 +1216,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62066120</v>
+        <v>121181611</v>
       </c>
       <c r="B7" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vägskälet 1, Jmt</t>
+          <t>Vilmyren, 200 m NO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472730.423935426</v>
+        <v>472560</v>
       </c>
       <c r="R7" t="n">
-        <v>7071107.92135937</v>
+        <v>7070988</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,27 +1281,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
+          <t>Urskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,31 +1306,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Sundin, Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62066123</v>
+        <v>62066120</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R8" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1451,27 +1383,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-07-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
+          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,16 +1404,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granlågor, asplåga,</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Granlågor, asplåga,</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1501,7 +1413,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
+          <t>Jörgen Sundin, Bengt Petterson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1512,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62066117</v>
+        <v>62066124</v>
       </c>
       <c r="B9" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R9" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1582,27 +1489,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
+          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,7 +1519,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Sundin, Bengt Petterson</t>
+          <t>Via Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1633,37 +1530,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62066119</v>
+        <v>62066121</v>
       </c>
       <c r="B10" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,13 +1565,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R10" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,19 +1598,9 @@
           <t>1994-07-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1757,16 +1639,11 @@
         <v>62066125</v>
       </c>
       <c r="B11" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1779,12 +1656,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1794,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R11" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1827,19 +1704,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1875,15 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62066122</v>
+        <v>121181483</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,37 +1753,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vägskälet 1, Jmt</t>
+          <t>Vilmyren, 200 m NO om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472730.423935426</v>
+        <v>472560</v>
       </c>
       <c r="R12" t="n">
-        <v>7071107.92135937</v>
+        <v>7070988</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1945,27 +1807,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1994-07-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, sumpskogen,</t>
+          <t>Urskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,31 +1832,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Sundin, Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>62066121</v>
+        <v>62066122</v>
       </c>
       <c r="B13" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R13" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2069,24 +1912,14 @@
           <t>1994-07-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1994-07-06</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, urskogsdelen,</t>
+          <t>Steget Före. Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg, sumpskogen,</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,37 +1950,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62066124</v>
+        <v>62103717</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2157,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R14" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2187,27 +2015,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området. Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
+          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området, Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,6 +2036,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2227,7 +2050,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2238,15 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62103717</v>
+        <v>121181487</v>
       </c>
       <c r="B15" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,17 +2092,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vägskälet 1, Jmt</t>
+          <t>Vilmyren, 200 m NO om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472730.423935426</v>
+        <v>472560</v>
       </c>
       <c r="R15" t="n">
-        <v>7071107.92135937</v>
+        <v>7070988</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2308,27 +2126,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1993-08-18</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1993-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området, Ullticka, rosenticka och rynkskinn på samma grova granlåga. Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
+          <t>Urskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,16 +2147,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -2356,23 +2159,14 @@
           <t>Bengt Petterson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>62103718</v>
       </c>
       <c r="B16" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472730.423935426</v>
+        <v>472730</v>
       </c>
       <c r="R16" t="n">
-        <v>7071107.92135937</v>
+        <v>7071108</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2437,19 +2231,9 @@
           <t>1993-08-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>1993-08-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2490,53 +2274,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62255426</v>
+        <v>121181486</v>
       </c>
       <c r="B17" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>620</v>
+        <v>2813</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vägskälet 1, Jmt</t>
+          <t>Vilmyren, 200 m NO om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472730.423935426</v>
+        <v>472560</v>
       </c>
       <c r="R17" t="n">
-        <v>7071107.92135937</v>
+        <v>7070988</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2560,27 +2339,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Avser det område som ingick i urskogsinventeringen. Delvis avverkat. Ny avgränsning skall göras som plockar in en angränsande brandrefugie med flera hotade arter. Delområden Vägskälet 1 nordost Hökbacktjärnen, Vägskälet 2 Margitbränna, dessutom finns Vägskälet 3 Björtjärns-området, Vägskälet 1, mellan Hökbacktjärnen och skogsbilväg,</t>
+          <t>Urskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,75 +2360,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121181611</v>
+        <v>61380396</v>
       </c>
       <c r="B18" t="n">
-        <v>91281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vilmyren, 200 m NO om, Jmt</t>
+          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472560</v>
+        <v>472730</v>
       </c>
       <c r="R18" t="n">
-        <v>7070988</v>
+        <v>7071108</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2686,17 +2441,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Urskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,15 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121181494</v>
+        <v>121181491</v>
       </c>
       <c r="B19" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2739,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2830,15 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121181495</v>
+        <v>60185565</v>
       </c>
       <c r="B20" t="n">
-        <v>98125</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,34 +2591,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vilmyren, 200 m NO om, Jmt</t>
+          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472560</v>
+        <v>472730</v>
       </c>
       <c r="R20" t="n">
-        <v>7070988</v>
+        <v>7071108</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2900,17 +2645,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Urskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,37 +2682,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121181484</v>
+        <v>121181494</v>
       </c>
       <c r="B21" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3044,50 +2784,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121181483</v>
+        <v>61047668</v>
       </c>
       <c r="B22" t="n">
-        <v>91159</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vilmyren, 200 m NO om, Jmt</t>
+          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472560</v>
+        <v>472730</v>
       </c>
       <c r="R22" t="n">
-        <v>7070988</v>
+        <v>7071108</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3114,17 +2849,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Urskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,15 +2886,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121181487</v>
+        <v>121181495</v>
       </c>
       <c r="B23" t="n">
-        <v>94506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,21 +2897,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3258,15 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121181491</v>
+        <v>61057592</v>
       </c>
       <c r="B24" t="n">
-        <v>105194</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99771</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,34 +2999,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vilmyren, 200 m NO om, Jmt</t>
+          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472560</v>
+        <v>472730</v>
       </c>
       <c r="R24" t="n">
-        <v>7070988</v>
+        <v>7071108</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3328,17 +3053,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Urskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,15 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121181486</v>
+        <v>121181493</v>
       </c>
       <c r="B25" t="n">
-        <v>94518</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99771</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,21 +3101,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2813</v>
+        <v>222302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3472,15 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121181493</v>
+        <v>61298441</v>
       </c>
       <c r="B26" t="n">
-        <v>98746</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,34 +3203,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222302</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vilmyren, 200 m NO om, Jmt</t>
+          <t>Vägskälet, mellan Hökbacktjärnen och skogsbilväg,, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472560</v>
+        <v>472730</v>
       </c>
       <c r="R26" t="n">
-        <v>7070988</v>
+        <v>7071108</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3542,17 +3257,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1993-08-08</t>
+          <t>1997-07-15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Urskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3582,12 +3297,7 @@
         <v>121181489</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 23434-2024 artfynd.xlsx
+++ b/artfynd/A 23434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62255426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066123</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066120</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066124</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066121</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066125</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181483</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1947,6 +2007,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62103717</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181487</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62103718</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181486</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2475,6 +2560,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61380396</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181491</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60185565</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2781,6 +2881,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181494</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2883,6 +2988,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61047668</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2985,6 +3095,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181495</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3087,6 +3202,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61057592</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181493</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3291,6 +3416,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298441</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,8 +3523,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121181489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>